--- a/reports/2026-02-23.xlsx
+++ b/reports/2026-02-23.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-23 05:41 UTC</t>
+          <t>2026-02-23 09:41 UTC</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -715,27 +715,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81.54000000000001</v>
+        <v>64.59</v>
       </c>
       <c r="F2" t="n">
-        <v>81.54000000000001</v>
+        <v>64.59</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$0.70</t>
+          <t>$0.71</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$1.73B</t>
+          <t>$1.75B</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>$4.24M</t>
+          <t>$4.53M</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -760,27 +760,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>81.01000000000001</v>
+        <v>62.77</v>
       </c>
       <c r="F3" t="n">
-        <v>81.01000000000001</v>
+        <v>62.77</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$2.20</t>
+          <t>$2.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$1.09B</t>
+          <t>$1.10B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>$1.39M</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -791,41 +791,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KITEUSDT</t>
+          <t>INJUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kite</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>64.8</v>
+        <v>50.02</v>
       </c>
       <c r="F4" t="n">
-        <v>64.8</v>
+        <v>50.02</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$0.26</t>
+          <t>$3.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$464.55M</t>
+          <t>$341.01M</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>$1.14M</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -836,12 +836,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -850,27 +850,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58.22</v>
+        <v>49.47</v>
       </c>
       <c r="F5" t="n">
-        <v>58.22</v>
+        <v>49.47</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$8.25</t>
+          <t>$248.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$5.85B</t>
+          <t>$4.08B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>$4.94M</t>
+          <t>$8.09M</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -881,41 +881,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TRUMPUSDT</t>
+          <t>PIPPINUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OFFICIAL TRUMP</t>
+          <t>pippin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58.18</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>58.18</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$3.27</t>
+          <t>$0.70</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$759.00M</t>
+          <t>$701.42M</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>$3.53M</t>
+          <t>$4.59M</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -926,12 +926,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAKEUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -940,27 +940,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>57.75</v>
+        <v>34.59</v>
       </c>
       <c r="F7" t="n">
-        <v>57.75</v>
+        <v>34.59</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$1.24</t>
+          <t>$8.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$484.68M</t>
+          <t>$3.75B</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>$1.25M</t>
+          <t>$14.04M</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -985,27 +985,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>57.53</v>
+        <v>33.11</v>
       </c>
       <c r="F8" t="n">
-        <v>57.53</v>
+        <v>33.11</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$8.43</t>
+          <t>$0.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$3.64B</t>
+          <t>$3.24B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>$12.89M</t>
+          <t>$19.27M</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1030,27 +1030,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57.43</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>57.43</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$0.26</t>
+          <t>$0.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$9.46B</t>
+          <t>$665.13M</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>$9.90M</t>
+          <t>$2.31M</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MNTUSDT</t>
+          <t>MXUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>MX Token</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1075,27 +1075,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57.12</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>57.12</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$0.59</t>
+          <t>$1.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$1.91B</t>
+          <t>$164.42M</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>$2.97M</t>
+          <t>$19.02M</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FILUSDT</t>
+          <t>MYXUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>MYX Finance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1120,27 +1120,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>56.69</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>56.69</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$0.89</t>
+          <t>$0.69</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$672.48M</t>
+          <t>$173.26M</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>$1.47M</t>
+          <t>$4.04M</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>BDXUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1165,27 +1165,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>56.63</v>
+        <v>29.78</v>
       </c>
       <c r="F12" t="n">
-        <v>56.63</v>
+        <v>29.78</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$0.88</t>
+          <t>$0.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>$3.38B</t>
+          <t>$609.77M</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>$16.83M</t>
+          <t>$1.13M</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEIUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sei</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1210,27 +1210,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>55.95</v>
+        <v>28.4</v>
       </c>
       <c r="F13" t="n">
-        <v>55.95</v>
+        <v>28.4</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$0.07</t>
+          <t>$3.47</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>$451.24M</t>
+          <t>$2.20B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>$1.33M</t>
+          <t>$5.45M</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WLDUSDT</t>
+          <t>LINKUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Worldcoin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1255,27 +1255,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>55.78</v>
+        <v>28.22</v>
       </c>
       <c r="F14" t="n">
-        <v>55.78</v>
+        <v>28.22</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$0.37</t>
+          <t>$8.47</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>$1.05B</t>
+          <t>$5.99B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>$2.29M</t>
+          <t>$5.29M</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PUMPUSDT</t>
+          <t>TRUMPUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pump.fun</t>
+          <t>OFFICIAL TRUMP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1300,27 +1300,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>55.33</v>
+        <v>28.18</v>
       </c>
       <c r="F15" t="n">
-        <v>55.33</v>
+        <v>28.18</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$0.00</t>
+          <t>$3.31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>$668.76M</t>
+          <t>$771.70M</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>$1.39M</t>
+          <t>$3.44M</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HBARUSDT</t>
+          <t>LTCUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1345,27 +1345,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>55.24</v>
+        <v>28.12</v>
       </c>
       <c r="F16" t="n">
-        <v>55.24</v>
+        <v>28.12</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$0.09</t>
+          <t>$52.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>$4.08B</t>
+          <t>$4.06B</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>$3.00M</t>
+          <t>$9.01M</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PENGUUSDT</t>
+          <t>HBARUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pudgy Penguins</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1390,27 +1390,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>54.12</v>
+        <v>28.09</v>
       </c>
       <c r="F17" t="n">
-        <v>54.12</v>
+        <v>28.09</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$0.01</t>
+          <t>$0.10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>$394.41M</t>
+          <t>$4.13B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>$1.81M</t>
+          <t>$3.44M</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DOTUSDT</t>
+          <t>TAOUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Bittensor</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1435,27 +1435,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54.03</v>
+        <v>28.08</v>
       </c>
       <c r="F18" t="n">
-        <v>54.03</v>
+        <v>28.08</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>$1.26</t>
+          <t>$171.87</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>$2.10B</t>
+          <t>$1.84B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>$3.14M</t>
+          <t>$3.93M</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DASHUSDT</t>
+          <t>CAKEUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dash</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1480,27 +1480,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53.67</v>
+        <v>27.75</v>
       </c>
       <c r="F19" t="n">
-        <v>53.67</v>
+        <v>27.75</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>$31.89</t>
+          <t>$1.27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>$401.56M</t>
+          <t>$419.97M</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>$2.87M</t>
+          <t>$1.31M</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ICPUSDT</t>
+          <t>NEARUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Internet Computer</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1525,27 +1525,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>52.71</v>
+        <v>27.73</v>
       </c>
       <c r="F20" t="n">
-        <v>52.71</v>
+        <v>27.73</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>$2.05</t>
+          <t>$1.01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>$1.13B</t>
+          <t>$1.31B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>$3.58M</t>
+          <t>$3.56M</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XMRUSDT</t>
+          <t>ADAUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1570,27 +1570,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>50.73</v>
+        <v>27.43</v>
       </c>
       <c r="F21" t="n">
-        <v>50.73</v>
+        <v>27.43</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$312.17</t>
+          <t>$0.27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>$5.76B</t>
+          <t>$9.75B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>$3.94M</t>
+          <t>$10.56M</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1702,21 +1702,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$0.70</t>
+          <t>$0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$1.73B</t>
+          <t>$1.75B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$4.24M</t>
+          <t>$4.53M</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>81.54000000000001</v>
+        <v>64.59</v>
       </c>
       <c r="H2" t="n">
         <v>98.31999999999999</v>
@@ -1728,7 +1728,7 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>97.37</v>
+        <v>40.87</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -1748,21 +1748,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$2.20</t>
+          <t>$2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$1.09B</t>
+          <t>$1.10B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$1.39M</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>81.01000000000001</v>
+        <v>62.77</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>90.38</v>
       </c>
       <c r="K3" t="n">
-        <v>60.79</v>
+        <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -1784,43 +1784,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LINKUSDT</t>
+          <t>INJUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>$8.25</t>
+          <t>$3.41</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$5.85B</t>
+          <t>$341.01M</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$4.94M</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>58.22</v>
+        <v>50.02</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>94.06</v>
+        <v>73.39</v>
       </c>
       <c r="J4" t="n">
+        <v>70</v>
+      </c>
+      <c r="K4" t="n">
         <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>100</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -1830,43 +1830,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TRUMPUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OFFICIAL TRUMP</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$3.27</t>
+          <t>$248.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$759.00M</t>
+          <t>$4.08B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$3.53M</t>
+          <t>$8.09M</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>58.18</v>
+        <v>49.47</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>93.94</v>
+        <v>67.75</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -1876,43 +1876,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CAKEUSDT</t>
+          <t>AVAXUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PancakeSwap</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>$1.24</t>
+          <t>$8.67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$484.68M</t>
+          <t>$3.75B</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$1.25M</t>
+          <t>$14.04M</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>57.75</v>
+        <v>34.59</v>
       </c>
       <c r="H6" t="n">
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>92.5</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>23.53</v>
       </c>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -1922,43 +1922,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AVAXUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$8.43</t>
+          <t>$0.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$3.64B</t>
+          <t>$3.24B</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$12.89M</t>
+          <t>$19.27M</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>57.53</v>
+        <v>33.11</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>91.76000000000001</v>
+        <v>79.84</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>3.86</v>
       </c>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -1968,37 +1968,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADAUSDT</t>
+          <t>MXUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>MX Token</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$0.26</t>
+          <t>$1.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$9.46B</t>
+          <t>$164.42M</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$9.90M</t>
+          <t>$19.02M</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>57.43</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>91.42</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2014,37 +2014,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MNTUSDT</t>
+          <t>MYXUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mantle</t>
+          <t>MYX Finance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$0.59</t>
+          <t>$0.69</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$1.91B</t>
+          <t>$173.26M</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$2.97M</t>
+          <t>$4.04M</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>57.12</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>64.73</v>
       </c>
       <c r="I9" t="n">
-        <v>90.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2060,37 +2060,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FILUSDT</t>
+          <t>APTUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Filecoin</t>
+          <t>Aptos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$0.89</t>
+          <t>$0.85</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$672.48M</t>
+          <t>$665.13M</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$1.47M</t>
+          <t>$2.31M</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>56.69</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>88.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2106,43 +2106,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUIUSDT</t>
+          <t>BDXUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sui</t>
+          <t>Beldex</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$0.88</t>
+          <t>$0.08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$3.38B</t>
+          <t>$609.77M</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$16.83M</t>
+          <t>$1.13M</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>56.63</v>
+        <v>29.78</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>88.76000000000001</v>
+        <v>99.28</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -2516,43 +2516,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KITEUSDT</t>
+          <t>ATOMUSDT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kite</t>
+          <t>Cosmos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>$0.26</t>
+          <t>$2.23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$464.55M</t>
+          <t>$1.10B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>$1.14M</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>64.8</v>
+        <v>58.08</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="J2" t="n">
-        <v>84</v>
+        <v>10.38</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -2562,40 +2562,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATOMUSDT</t>
+          <t>ASTERUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cosmos</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>$2.20</t>
+          <t>$0.71</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$1.09B</t>
+          <t>$1.75B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$1.39M</t>
+          <t>$4.53M</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>58.08</v>
+        <v>49.6</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>10.38</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>80</v>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASTERUSDT</t>
+          <t>PIPPINUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>pippin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2623,28 +2623,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$1.73B</t>
+          <t>$701.42M</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$4.24M</t>
+          <t>$4.59M</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>48</v>
       </c>
       <c r="H4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I4" t="n">
         <v>20</v>
       </c>
-      <c r="I4" t="n">
-        <v>100</v>
-      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>30.54</v>
       </c>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -2654,45 +2654,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PIPPINUSDT</t>
+          <t>HBARUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pippin</t>
+          <t>Hedera</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>$0.66</t>
+          <t>$0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$656.37M</t>
+          <t>$4.13B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$5.04M</t>
+          <t>$3.44M</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>41.6</v>
+        <v>20.8</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>broken_trend</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2715,16 +2719,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$609.17M</t>
+          <t>$609.77M</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$1.09M</t>
+          <t>$1.13M</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2733,7 +2737,7 @@
         <v>100</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -2750,43 +2754,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HBARUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hedera</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>$0.09</t>
+          <t>$28.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$4.08B</t>
+          <t>$7.24B</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$3.00M</t>
+          <t>$5.54M</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>20.8</v>
+        <v>16.8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J7" t="n">
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>22.19</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2800,43 +2804,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HYPEUSDT</t>
+          <t>ZROUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>LayerZero</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>$27.57</t>
+          <t>$1.60</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$7.13B</t>
+          <t>$482.05M</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$4.49M</t>
+          <t>$3.22M</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>16.8</v>
+        <v>10.4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>2.15</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2850,43 +2854,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZROUSDT</t>
+          <t>INJUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LayerZero</t>
+          <t>Injective</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$1.51</t>
+          <t>$3.41</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$454.91M</t>
+          <t>$341.01M</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>$2.96M</t>
+          <t>$1.52M</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="K9" t="n">
-        <v>27.93</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2900,31 +2904,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INJUSDT</t>
+          <t>WLFIUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Injective</t>
+          <t>World Liberty Financial</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$3.42</t>
+          <t>$0.12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$341.29M</t>
+          <t>$3.24B</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>$1.69M</t>
+          <t>$19.27M</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2933,10 +2937,10 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>25.79</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2950,31 +2954,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WLFIUSDT</t>
+          <t>UNIUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>World Liberty Financial</t>
+          <t>Uniswap</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$0.11</t>
+          <t>$3.47</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$3.14B</t>
+          <t>$2.20B</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$18.88M</t>
+          <t>$5.45M</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -2983,10 +2987,10 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>25.79</v>
+        <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
